--- a/英语群_20260831.xlsx
+++ b/英语群_20260831.xlsx
@@ -1258,7 +1258,7 @@
       </c>
       <c r="C1" s="24">
         <f>SUM(C3:C1001)</f>
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D1" s="24">
         <f>SUM(D3:D1001)</f>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="E1" s="24">
         <f>SUM(E3:E1001)</f>
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F1" s="11" t="s">
         <v>0</v>
@@ -1494,21 +1494,21 @@
       </c>
       <c r="C7" s="3">
         <f t="shared" si="1"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" s="3">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E7" s="3">
         <f t="shared" si="3"/>
         <v>8</v>
       </c>
       <c r="F7" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="5">
         <v>0</v>
@@ -1578,24 +1578,24 @@
       </c>
       <c r="C9" s="3">
         <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="D9" s="3">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="E9" s="3">
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
-      <c r="D9" s="3">
-        <f t="shared" si="2"/>
-        <v>8</v>
-      </c>
-      <c r="E9" s="3">
-        <f t="shared" si="3"/>
-        <v>9</v>
-      </c>
       <c r="F9" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="5">
         <v>0</v>
       </c>
       <c r="H9" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I9" s="25">
         <v>26</v>
@@ -1834,20 +1834,20 @@
       </c>
       <c r="D15" s="3">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" s="3">
         <f t="shared" si="3"/>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F15" s="5">
         <v>0</v>
       </c>
       <c r="G15" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" s="25">
         <v>30</v>
@@ -2040,21 +2040,21 @@
       </c>
       <c r="C20" s="3">
         <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="D20" s="3">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="E20" s="3">
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="D20" s="3">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-      <c r="E20" s="3">
-        <f t="shared" si="3"/>
-        <v>8</v>
-      </c>
       <c r="F20" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" s="5">
         <v>0</v>
@@ -2250,24 +2250,24 @@
       </c>
       <c r="C25" s="3">
         <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="D25" s="3">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="E25" s="3">
+        <f t="shared" si="3"/>
         <v>8</v>
       </c>
-      <c r="D25" s="3">
-        <f t="shared" si="2"/>
-        <v>10</v>
-      </c>
-      <c r="E25" s="3">
-        <f t="shared" si="3"/>
-        <v>7</v>
-      </c>
       <c r="F25" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" s="5">
         <v>0</v>
       </c>
       <c r="H25" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" s="25">
         <v>24</v>
@@ -2338,20 +2338,20 @@
       </c>
       <c r="D27" s="3">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E27" s="3">
         <f t="shared" si="3"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F27" s="5">
         <v>0</v>
       </c>
       <c r="G27" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I27" s="25">
         <v>11</v>
@@ -2418,21 +2418,21 @@
       </c>
       <c r="C29" s="3">
         <f t="shared" si="1"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D29" s="3">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E29" s="3">
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
       <c r="F29" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G29" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" s="5">
         <v>0</v>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="C30" s="3">
         <f t="shared" si="1"/>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D30" s="3">
         <f t="shared" si="2"/>
@@ -2468,16 +2468,16 @@
       </c>
       <c r="E30" s="3">
         <f t="shared" si="3"/>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F30" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" s="5">
         <v>0</v>
       </c>
       <c r="H30" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I30" s="25">
         <v>30</v>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C35" s="3">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D35" s="3">
         <f t="shared" si="2"/>
@@ -2678,16 +2678,16 @@
       </c>
       <c r="E35" s="3">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F35" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" s="5">
         <v>0</v>
       </c>
       <c r="H35" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" s="25">
         <v>29</v>
@@ -2842,20 +2842,20 @@
       </c>
       <c r="D39" s="3">
         <f t="shared" si="2"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E39" s="3">
         <f t="shared" si="3"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F39" s="5">
         <v>0</v>
       </c>
       <c r="G39" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H39" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I39" s="25">
         <v>25</v>
@@ -3216,21 +3216,21 @@
       </c>
       <c r="C48" s="3">
         <f t="shared" si="1"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D48" s="3">
         <f t="shared" si="2"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E48" s="3">
         <f t="shared" si="3"/>
         <v>12</v>
       </c>
       <c r="F48" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G48" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" s="5">
         <v>0</v>
@@ -3262,20 +3262,20 @@
       </c>
       <c r="D49" s="3">
         <f t="shared" si="2"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E49" s="3">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F49" s="5">
         <v>0</v>
       </c>
       <c r="G49" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I49" s="25">
         <v>28</v>
